--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（51家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（33家）" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（25条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -478,7 +478,7 @@
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,23 +719,23 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>-18</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-100.0%</t>
+      <c r="C12" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -875,14 +875,14 @@
         <v>8734</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8701</v>
+        <v>8719</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-33</v>
+        <v>-15</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
@@ -6332,297 +6332,297 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="inlineStr">
+      <c r="A259" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B259" s="2" t="inlineStr">
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E259" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E260" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E262" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E265" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D266" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E266" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
         <is>
           <t>浙江</t>
         </is>
       </c>
-      <c r="C259" s="2" t="n">
+      <c r="C267" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D259" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E259" s="2" t="n">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
+      <c r="D267" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E267" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D260" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E260" s="2" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E268" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C261" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D261" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E261" s="2" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D269" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E269" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B262" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C262" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D262" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E262" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B263" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C263" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D263" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E263" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C264" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D264" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E264" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B265" s="2" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C265" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D265" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E265" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B266" s="2" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C266" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D266" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E266" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B267" s="2" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C267" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D267" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E267" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D268" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E268" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B269" s="2" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C269" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D269" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E269" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B270" s="2" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C270" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D270" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E270" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B271" s="2" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="C271" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D271" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E271" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B272" s="2" t="inlineStr">
+      <c r="B272" s="3" t="inlineStr">
         <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C272" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D272" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E272" s="2" t="n">
-        <v>-1</v>
+      <c r="C272" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
     </row>
@@ -11314,174 +11314,174 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>意特汽车商业（上海）有限公司</t>
+          <t>深圳罗湖KKMALL体验店</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>恒通东路69号101单元 龙盛福新汇 上海 上海</t>
+          <t>广东省深圳市罗湖区桂园街道深南东路5016号KKMALL一层L112/112A3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>昆明乐骏汽车销售服务有限公司</t>
+          <t>贵阳方圆荟海豚广场</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>昆明市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>滇池度假区滇池路1103号平安大厦B座1层 平安大厦 昆明市 滇池度假区</t>
+          <t>贵州省贵阳市南明区花果园大街88号1F-SN007铺位</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>北京骏东汽车销售服务有限公司</t>
+          <t>西安曲江大悦城体验店</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>西安市</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>金宝街 金宝大厦一层 北京 东城区</t>
+          <t>陕西省西安市雁塔区慈恩西路777号</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>成都骏意汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>成都市</t>
+          <t>威海市</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>成都市高新区火车南站西路 法拉利 成都市 中国</t>
+          <t>山东省威海市环翠区经技技术开发区青岛南路242号</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>安徽鸿粤鸿超汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>合肥市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>花亭湖路与齐云山路交叉口 安徽鸿粤鸿超汽车销售服务有限公司 合肥 蜀山区</t>
+          <t>山西省晋中市山西综改示范区晋中开发区汇通产业园区汇通北路1060号</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>青岛恒骏汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•东莞虎门鸿熙汽车城</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>东莞市</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>青岛市市南区东海西路1号1号楼丙户 青岛市 市南区</t>
+          <t>广东省东莞市虎门镇博涌社区社岗村S358省道旁</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>广东骏佳汽车服务有限公司</t>
+          <t>华为授权体验店（新塘永旺）</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -11495,492 +11495,6 @@
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>天河区珠江新城清风街1-48号 新世界广场首层 Guangzhou</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>骏佳行汽车服务（深圳）有限公司</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>深圳市</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>中心路1号 深圳湾壹号北区2栋 Shenzhen Nanshan District</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>南京瑞骏汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>南京市</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>长江路100号 长江会 南京 玄武</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>苏州意骏汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>苏州市</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>苏州工业园区思安街99号协鑫广场西侧1F Suzhou</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>宁波骏意汽车服务有限公司</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>宁波市</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>中官新路 A号楼 Ningbo Jiangbei District</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>杭州骏意汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>杭州市</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>浙江省杭州市南山路 杭州 上城区</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>温州骏意汽车服务有限公司</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>温州市</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>温州经济技术开发区滨海园区 3号4S店东侧 温州 中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>武汉骏东汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>武汉市</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>解放大道634号K11步行街 108-109 武汉 中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>长沙市骏马汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>长沙市</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>潇湘北路 圆泰长沙印 103-1 号 长沙市 中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>福建骏佳行汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>厦门市</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>环岛东路1821号 中航紫金广场商业街 厦门市 思明区</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>重庆骏东汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>重庆两江新区新南路 龙湖晶郦馆A栋-1F-03b Chongqing New South St</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>西安市</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>深圳罗湖KKMALL体验店</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>深圳市</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>广东省深圳市罗湖区桂园街道深南东路5016号KKMALL一层L112/112A3</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>贵阳方圆荟海豚广场</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>贵阳市</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>贵州省贵阳市南明区花果园大街88号1F-SN007铺位</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>西安曲江大悦城体验店</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>西安市</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>陕西省西安市雁塔区慈恩西路777号</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>威海市</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>山东省威海市环翠区经技技术开发区青岛南路242号</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>晋中市</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>山西省晋中市山西综改示范区晋中开发区汇通产业园区汇通北路1060号</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•东莞虎门鸿熙汽车城</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>东莞市</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>广东省东莞市虎门镇博涌社区社岗村S358省道旁</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>华为授权体验店（新塘永旺）</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>广东省广州市增城区新塘永旺1楼华为授权体验店（西町村屋对面）</t>
         </is>
@@ -12043,22 +11557,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12068,29 +11582,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12100,29 +11614,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12132,7 +11646,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -12171,22 +11685,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12196,7 +11710,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
@@ -12235,22 +11749,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12260,29 +11774,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12292,29 +11806,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12324,29 +11838,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12356,7 +11870,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -12368,17 +11882,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12388,29 +11902,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12420,29 +11934,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12452,29 +11966,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12484,29 +11998,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12516,7 +12030,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
@@ -12555,22 +12069,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12587,22 +12101,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12619,22 +12133,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12651,7 +12165,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -12661,12 +12175,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12693,12 +12207,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12715,7 +12229,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -12725,12 +12239,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12747,22 +12261,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12779,22 +12293,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
     </row>
@@ -11557,22 +11557,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
@@ -11594,17 +11594,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11614,29 +11614,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11658,17 +11658,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11678,29 +11678,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11710,29 +11710,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11742,29 +11742,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -11786,17 +11786,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11806,29 +11806,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11838,29 +11838,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11870,29 +11870,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -11914,17 +11914,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -11973,22 +11973,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11998,29 +11998,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -12069,22 +12069,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12101,22 +12101,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12133,22 +12133,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12165,22 +12165,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12207,12 +12207,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12234,17 +12234,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12261,22 +12261,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -11557,22 +11557,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
@@ -11594,17 +11594,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11614,14 +11614,14 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -11631,12 +11631,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11646,29 +11646,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11678,29 +11678,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11710,29 +11710,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11742,29 +11742,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11774,29 +11774,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11806,29 +11806,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11838,29 +11838,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11870,29 +11870,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11902,29 +11902,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11934,29 +11934,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11966,29 +11966,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11998,29 +11998,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
@@ -12069,22 +12069,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12101,22 +12101,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12133,22 +12133,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12165,22 +12165,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12202,17 +12202,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12234,17 +12234,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12261,22 +12261,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
     </row>
@@ -11557,22 +11557,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11582,29 +11582,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11614,29 +11614,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -11717,22 +11717,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11742,29 +11742,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11774,29 +11774,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11806,29 +11806,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11838,14 +11838,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11870,29 +11870,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11902,29 +11902,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
@@ -11978,17 +11978,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11998,29 +11998,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
@@ -12069,22 +12069,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12101,7 +12101,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12133,22 +12133,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12197,22 +12197,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12229,22 +12229,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12266,17 +12266,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12293,7 +12293,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -11557,22 +11557,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11582,29 +11582,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
@@ -11626,17 +11626,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
@@ -11658,17 +11658,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11678,29 +11678,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -11749,22 +11749,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11774,29 +11774,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
@@ -11818,17 +11818,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11838,29 +11838,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11870,29 +11870,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11914,17 +11914,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11934,29 +11934,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11966,29 +11966,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11998,29 +11998,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -12069,22 +12069,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12101,7 +12101,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12165,22 +12165,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12197,22 +12197,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12229,22 +12229,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12298,17 +12298,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
     </row>
@@ -11557,22 +11557,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11582,14 +11582,14 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -11599,12 +11599,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11614,29 +11614,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11646,29 +11646,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -11690,17 +11690,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11710,29 +11710,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11742,29 +11742,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11774,29 +11774,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11806,29 +11806,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -11850,17 +11850,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11870,29 +11870,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11902,29 +11902,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11934,29 +11934,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11966,29 +11966,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11998,29 +11998,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -12074,17 +12074,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12101,22 +12101,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12165,22 +12165,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12197,7 +12197,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -12207,12 +12207,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12229,7 +12229,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -12239,12 +12239,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12261,22 +12261,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12298,17 +12298,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
     </row>
@@ -11557,22 +11557,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -11594,17 +11594,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11614,29 +11614,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11646,29 +11646,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
@@ -11717,22 +11717,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11742,29 +11742,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11774,29 +11774,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11806,29 +11806,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
@@ -11850,17 +11850,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11870,29 +11870,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11941,22 +11941,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -11978,17 +11978,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
@@ -12069,22 +12069,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12101,22 +12101,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12138,17 +12138,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12165,7 +12165,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12229,22 +12229,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12261,22 +12261,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（33家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（25条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（33家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（25条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
     </row>
@@ -11557,22 +11557,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11582,29 +11582,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11614,29 +11614,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11646,29 +11646,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
@@ -11690,17 +11690,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
@@ -11722,17 +11722,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11742,29 +11742,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11774,29 +11774,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11806,29 +11806,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11838,29 +11838,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11870,14 +11870,14 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -11887,12 +11887,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
@@ -11914,17 +11914,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11934,29 +11934,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -11978,17 +11978,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11998,29 +11998,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -12069,22 +12069,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12101,22 +12101,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12133,22 +12133,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12165,22 +12165,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12207,12 +12207,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12229,22 +12229,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12261,7 +12261,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -12271,12 +12271,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（33家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（25条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（33家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（25条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
     </row>
@@ -11557,22 +11557,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11582,29 +11582,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11614,29 +11614,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11646,29 +11646,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11678,29 +11678,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11710,29 +11710,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11742,29 +11742,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11774,29 +11774,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11806,29 +11806,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11838,29 +11838,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11870,14 +11870,14 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -11887,12 +11887,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11902,29 +11902,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11934,29 +11934,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11966,29 +11966,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11998,29 +11998,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12101,22 +12101,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12133,22 +12133,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12170,17 +12170,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12197,22 +12197,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12229,22 +12229,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12261,7 +12261,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -12271,12 +12271,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12293,7 +12293,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（33家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（25条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（33家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（25条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
     </row>
@@ -11557,22 +11557,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11582,29 +11582,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
@@ -11653,22 +11653,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11678,29 +11678,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11710,29 +11710,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11742,29 +11742,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -11813,22 +11813,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -11850,17 +11850,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -11882,17 +11882,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -11914,17 +11914,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11934,29 +11934,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11978,17 +11978,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11998,29 +11998,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12069,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12133,22 +12133,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12170,17 +12170,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12197,22 +12197,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12229,22 +12229,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12261,22 +12261,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12293,22 +12293,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（33家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（25条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（33家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（25条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
     </row>
@@ -11589,22 +11589,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -11653,22 +11653,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
@@ -11690,17 +11690,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
@@ -11722,17 +11722,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11742,29 +11742,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11774,29 +11774,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11806,29 +11806,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
@@ -11850,17 +11850,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
@@ -11909,22 +11909,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11934,29 +11934,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -12005,7 +12005,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -12015,12 +12015,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -12069,22 +12069,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12133,22 +12133,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12197,22 +12197,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12229,7 +12229,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -12239,12 +12239,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12266,17 +12266,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12293,22 +12293,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -11589,22 +11589,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11614,29 +11614,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
@@ -11717,22 +11717,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11742,29 +11742,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11774,29 +11774,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
@@ -11845,22 +11845,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11870,29 +11870,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11902,29 +11902,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11934,29 +11934,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11978,17 +11978,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -12010,17 +12010,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -12069,22 +12069,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12101,7 +12101,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12133,22 +12133,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12165,22 +12165,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12197,22 +12197,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12229,22 +12229,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12261,22 +12261,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12293,22 +12293,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8734</v>
+        <v>8736</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8719</v>
+        <v>8721</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-15</v>
@@ -897,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E434"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6507,14 +6507,14 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D267" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E267" s="3" t="n">
         <v>0</v>
@@ -6528,14 +6528,14 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D268" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E268" s="3" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -6612,59 +6612,59 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C272" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D272" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E272" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B273" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C273" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="D273" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="E273" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D274" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E274" s="2" t="n">
-        <v>-1</v>
+      <c r="C274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -6675,59 +6675,59 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C275" s="2" t="n">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D275" s="2" t="n">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="E275" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="3" t="inlineStr">
+      <c r="A276" s="2" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B276" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C276" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="D276" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="E276" s="3" t="n">
-        <v>0</v>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D276" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="3" t="inlineStr">
+      <c r="A277" s="2" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B277" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C277" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D277" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E277" s="3" t="n">
-        <v>0</v>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D277" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="278">
@@ -6738,14 +6738,14 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="D278" s="3" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="E278" s="3" t="n">
         <v>0</v>
@@ -6759,14 +6759,14 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D279" s="3" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E279" s="3" t="n">
         <v>0</v>
@@ -6780,14 +6780,14 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D280" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E280" s="3" t="n">
         <v>0</v>
@@ -6801,14 +6801,14 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D281" s="3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E281" s="3" t="n">
         <v>0</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D282" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E282" s="3" t="n">
         <v>0</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C283" s="3" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E283" s="3" t="n">
         <v>0</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D284" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E284" s="3" t="n">
         <v>0</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D285" s="3" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E285" s="3" t="n">
         <v>0</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D286" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E286" s="3" t="n">
         <v>0</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D287" s="3" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E287" s="3" t="n">
         <v>0</v>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
@@ -6969,14 +6969,14 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D289" s="3" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="E289" s="3" t="n">
         <v>0</v>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D290" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E290" s="3" t="n">
         <v>0</v>
@@ -7011,14 +7011,14 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="D291" s="3" t="n">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="E291" s="3" t="n">
         <v>0</v>
@@ -7032,14 +7032,14 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D292" s="3" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E292" s="3" t="n">
         <v>0</v>
@@ -7053,14 +7053,14 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="D293" s="3" t="n">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="E293" s="3" t="n">
         <v>0</v>
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C294" s="3" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D294" s="3" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E294" s="3" t="n">
         <v>0</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="D295" s="3" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="E295" s="3" t="n">
         <v>0</v>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D296" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E296" s="3" t="n">
         <v>0</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D297" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E297" s="3" t="n">
         <v>0</v>
@@ -7158,14 +7158,14 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D298" s="3" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E298" s="3" t="n">
         <v>0</v>
@@ -7179,14 +7179,14 @@
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C299" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D299" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E299" s="3" t="n">
         <v>0</v>
@@ -7200,14 +7200,14 @@
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C300" s="3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D300" s="3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E300" s="3" t="n">
         <v>0</v>
@@ -7221,14 +7221,14 @@
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D301" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E301" s="3" t="n">
         <v>0</v>
@@ -7242,14 +7242,14 @@
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C302" s="3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D302" s="3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E302" s="3" t="n">
         <v>0</v>
@@ -7258,19 +7258,19 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C303" s="3" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D303" s="3" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E303" s="3" t="n">
         <v>0</v>
@@ -7279,19 +7279,19 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C304" s="3" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D304" s="3" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E304" s="3" t="n">
         <v>0</v>
@@ -7305,14 +7305,14 @@
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C305" s="3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D305" s="3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E305" s="3" t="n">
         <v>0</v>
@@ -7326,14 +7326,14 @@
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C306" s="3" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D306" s="3" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E306" s="3" t="n">
         <v>0</v>
@@ -7347,14 +7347,14 @@
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C307" s="3" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D307" s="3" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E307" s="3" t="n">
         <v>0</v>
@@ -7368,14 +7368,14 @@
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C308" s="3" t="n">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="D308" s="3" t="n">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="E308" s="3" t="n">
         <v>0</v>
@@ -7389,14 +7389,14 @@
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C309" s="3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D309" s="3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E309" s="3" t="n">
         <v>0</v>
@@ -7410,14 +7410,14 @@
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C310" s="3" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="D310" s="3" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="E310" s="3" t="n">
         <v>0</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C311" s="3" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="D311" s="3" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="E311" s="3" t="n">
         <v>0</v>
@@ -7452,14 +7452,14 @@
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C312" s="3" t="n">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="D312" s="3" t="n">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="E312" s="3" t="n">
         <v>0</v>
@@ -7473,14 +7473,14 @@
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C313" s="3" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D313" s="3" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E313" s="3" t="n">
         <v>0</v>
@@ -7494,14 +7494,14 @@
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C314" s="3" t="n">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="D314" s="3" t="n">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="E314" s="3" t="n">
         <v>0</v>
@@ -7515,14 +7515,14 @@
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D315" s="3" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E315" s="3" t="n">
         <v>0</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C316" s="3" t="n">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="D316" s="3" t="n">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="E316" s="3" t="n">
         <v>0</v>
@@ -7557,14 +7557,14 @@
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="D317" s="3" t="n">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="E317" s="3" t="n">
         <v>0</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C318" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D318" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E318" s="3" t="n">
         <v>0</v>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="D319" s="3" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="E319" s="3" t="n">
         <v>0</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="D320" s="3" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="E320" s="3" t="n">
         <v>0</v>
@@ -7641,14 +7641,14 @@
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="D321" s="3" t="n">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="E321" s="3" t="n">
         <v>0</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="D322" s="3" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="E322" s="3" t="n">
         <v>0</v>
@@ -7683,14 +7683,14 @@
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="D323" s="3" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="E323" s="3" t="n">
         <v>0</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C324" s="3" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D324" s="3" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E324" s="3" t="n">
         <v>0</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D325" s="3" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="E325" s="3" t="n">
         <v>0</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C326" s="3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D326" s="3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E326" s="3" t="n">
         <v>0</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D327" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E327" s="3" t="n">
         <v>0</v>
@@ -7788,14 +7788,14 @@
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D328" s="3" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E328" s="3" t="n">
         <v>0</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D329" s="3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E329" s="3" t="n">
         <v>0</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C330" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D330" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E330" s="3" t="n">
         <v>0</v>
@@ -7851,14 +7851,14 @@
       </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C331" s="3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D331" s="3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E331" s="3" t="n">
         <v>0</v>
@@ -7872,14 +7872,14 @@
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C332" s="3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D332" s="3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E332" s="3" t="n">
         <v>0</v>
@@ -7893,14 +7893,14 @@
       </c>
       <c r="B333" s="3" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C333" s="3" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D333" s="3" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E333" s="3" t="n">
         <v>0</v>
@@ -7909,19 +7909,19 @@
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C334" s="3" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="D334" s="3" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="E334" s="3" t="n">
         <v>0</v>
@@ -7930,19 +7930,19 @@
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B335" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C335" s="3" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D335" s="3" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E335" s="3" t="n">
         <v>0</v>
@@ -7956,14 +7956,14 @@
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C336" s="3" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D336" s="3" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="E336" s="3" t="n">
         <v>0</v>
@@ -7977,14 +7977,14 @@
       </c>
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C337" s="3" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D337" s="3" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E337" s="3" t="n">
         <v>0</v>
@@ -7998,14 +7998,14 @@
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D338" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E338" s="3" t="n">
         <v>0</v>
@@ -8019,14 +8019,14 @@
       </c>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C339" s="3" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D339" s="3" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E339" s="3" t="n">
         <v>0</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C340" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D340" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E340" s="3" t="n">
         <v>0</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C341" s="3" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D341" s="3" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E341" s="3" t="n">
         <v>0</v>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C342" s="3" t="n">
@@ -8103,14 +8103,14 @@
       </c>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="D343" s="3" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="E343" s="3" t="n">
         <v>0</v>
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C344" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D344" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E344" s="3" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C345" s="3" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="D345" s="3" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="E345" s="3" t="n">
         <v>0</v>
@@ -8166,14 +8166,14 @@
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D346" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E346" s="3" t="n">
         <v>0</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C347" s="3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D347" s="3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E347" s="3" t="n">
         <v>0</v>
@@ -8208,14 +8208,14 @@
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D348" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E348" s="3" t="n">
         <v>0</v>
@@ -8229,14 +8229,14 @@
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D349" s="3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E349" s="3" t="n">
         <v>0</v>
@@ -8250,14 +8250,14 @@
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D350" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E350" s="3" t="n">
         <v>0</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D351" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E351" s="3" t="n">
         <v>0</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D352" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E352" s="3" t="n">
         <v>0</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D353" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E353" s="3" t="n">
         <v>0</v>
@@ -8334,14 +8334,14 @@
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D354" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E354" s="3" t="n">
         <v>0</v>
@@ -8355,14 +8355,14 @@
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D355" s="3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E355" s="3" t="n">
         <v>0</v>
@@ -8376,14 +8376,14 @@
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C356" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D356" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E356" s="3" t="n">
         <v>0</v>
@@ -8397,14 +8397,14 @@
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C357" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D357" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E357" s="3" t="n">
         <v>0</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C358" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D358" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E358" s="3" t="n">
         <v>0</v>
@@ -8439,59 +8439,59 @@
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C359" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D359" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E359" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="3" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B360" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C360" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D360" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E360" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="3" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B361" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C359" s="3" t="n">
+      <c r="C361" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D359" s="3" t="n">
+      <c r="D361" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E359" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" s="4" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B360" s="4" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C360" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="D360" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E360" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" s="4" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B361" s="4" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C361" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D361" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E361" s="4" t="n">
-        <v>1</v>
+      <c r="E361" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="362">
@@ -8502,14 +8502,14 @@
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C362" s="4" t="n">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="D362" s="4" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="E362" s="4" t="n">
         <v>1</v>
@@ -8523,59 +8523,59 @@
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C363" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D363" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="E363" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="4" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B364" s="4" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C364" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="D364" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="E364" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="4" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B365" s="4" t="inlineStr">
+        <is>
           <t>浙江</t>
         </is>
       </c>
-      <c r="C363" s="4" t="n">
+      <c r="C365" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="D363" s="4" t="n">
+      <c r="D365" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="E363" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" s="3" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁</t>
-        </is>
-      </c>
-      <c r="B364" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C364" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D364" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E364" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" s="3" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁</t>
-        </is>
-      </c>
-      <c r="B365" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C365" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D365" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E365" s="3" t="n">
-        <v>0</v>
+      <c r="E365" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="366">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C366" s="3" t="n">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="B367" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C367" s="3" t="n">
@@ -8628,14 +8628,14 @@
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C368" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D368" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E368" s="3" t="n">
         <v>0</v>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="B369" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C369" s="3" t="n">
@@ -8670,14 +8670,14 @@
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C370" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D370" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E370" s="3" t="n">
         <v>0</v>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C371" s="3" t="n">
@@ -8712,14 +8712,14 @@
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C372" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D372" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E372" s="3" t="n">
         <v>0</v>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C373" s="3" t="n">
@@ -8749,19 +8749,19 @@
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C374" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D374" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E374" s="3" t="n">
         <v>0</v>
@@ -8770,19 +8770,19 @@
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B375" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C375" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D375" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E375" s="3" t="n">
         <v>0</v>
@@ -8796,14 +8796,14 @@
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C376" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D376" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E376" s="3" t="n">
         <v>0</v>
@@ -8817,14 +8817,14 @@
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C377" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D377" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E377" s="3" t="n">
         <v>0</v>
@@ -8838,14 +8838,14 @@
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C378" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D378" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E378" s="3" t="n">
         <v>0</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C379" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D379" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E379" s="3" t="n">
         <v>0</v>
@@ -8880,14 +8880,14 @@
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C380" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D380" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E380" s="3" t="n">
         <v>0</v>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C381" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D381" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E381" s="3" t="n">
         <v>0</v>
@@ -8922,14 +8922,14 @@
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C382" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D382" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E382" s="3" t="n">
         <v>0</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C383" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D383" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E383" s="3" t="n">
         <v>0</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C384" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D384" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E384" s="3" t="n">
         <v>0</v>
@@ -8985,14 +8985,14 @@
       </c>
       <c r="B385" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C385" s="3" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="D385" s="3" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="E385" s="3" t="n">
         <v>0</v>
@@ -9006,14 +9006,14 @@
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C386" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D386" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E386" s="3" t="n">
         <v>0</v>
@@ -9027,14 +9027,14 @@
       </c>
       <c r="B387" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C387" s="3" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="D387" s="3" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="E387" s="3" t="n">
         <v>0</v>
@@ -9048,14 +9048,14 @@
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C388" s="3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D388" s="3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E388" s="3" t="n">
         <v>0</v>
@@ -9069,14 +9069,14 @@
       </c>
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C389" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D389" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E389" s="3" t="n">
         <v>0</v>
@@ -9090,14 +9090,14 @@
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C390" s="3" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D390" s="3" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E390" s="3" t="n">
         <v>0</v>
@@ -9111,14 +9111,14 @@
       </c>
       <c r="B391" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C391" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D391" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E391" s="3" t="n">
         <v>0</v>
@@ -9132,14 +9132,14 @@
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C392" s="3" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D392" s="3" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E392" s="3" t="n">
         <v>0</v>
@@ -9153,14 +9153,14 @@
       </c>
       <c r="B393" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C393" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D393" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E393" s="3" t="n">
         <v>0</v>
@@ -9174,14 +9174,14 @@
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C394" s="3" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D394" s="3" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E394" s="3" t="n">
         <v>0</v>
@@ -9195,14 +9195,14 @@
       </c>
       <c r="B395" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C395" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D395" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E395" s="3" t="n">
         <v>0</v>
@@ -9216,14 +9216,14 @@
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C396" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D396" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E396" s="3" t="n">
         <v>0</v>
@@ -9237,14 +9237,14 @@
       </c>
       <c r="B397" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C397" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D397" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E397" s="3" t="n">
         <v>0</v>
@@ -9258,14 +9258,14 @@
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C398" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D398" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E398" s="3" t="n">
         <v>0</v>
@@ -9279,14 +9279,14 @@
       </c>
       <c r="B399" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C399" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D399" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E399" s="3" t="n">
         <v>0</v>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C400" s="3" t="n">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="B401" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C401" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D401" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E401" s="3" t="n">
         <v>0</v>
@@ -9342,14 +9342,14 @@
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C402" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D402" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E402" s="3" t="n">
         <v>0</v>
@@ -9363,59 +9363,59 @@
       </c>
       <c r="B403" s="3" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C403" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D403" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E403" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="3" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C404" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E404" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="3" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C403" s="3" t="n">
+      <c r="C405" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D403" s="3" t="n">
+      <c r="D405" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E403" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B404" s="2" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C404" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="D404" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E404" s="2" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B405" s="2" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C405" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="D405" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="E405" s="2" t="n">
-        <v>-1</v>
+      <c r="E405" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -9426,59 +9426,59 @@
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C406" s="2" t="n">
-        <v>205</v>
+        <v>101</v>
       </c>
       <c r="D406" s="2" t="n">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="E406" s="2" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="3" t="inlineStr">
+      <c r="A407" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B407" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C407" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="D407" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="E407" s="3" t="n">
-        <v>0</v>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="D407" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="E407" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="3" t="inlineStr">
+      <c r="A408" s="2" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B408" s="3" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C408" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="D408" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="E408" s="3" t="n">
-        <v>0</v>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="D408" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="E408" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="409">
@@ -9489,14 +9489,14 @@
       </c>
       <c r="B409" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C409" s="3" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D409" s="3" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E409" s="3" t="n">
         <v>0</v>
@@ -9510,14 +9510,14 @@
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C410" s="3" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D410" s="3" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E410" s="3" t="n">
         <v>0</v>
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C411" s="3" t="n">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="D411" s="3" t="n">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="E411" s="3" t="n">
         <v>0</v>
@@ -9552,14 +9552,14 @@
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C412" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D412" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E412" s="3" t="n">
         <v>0</v>
@@ -9573,14 +9573,14 @@
       </c>
       <c r="B413" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C413" s="3" t="n">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="D413" s="3" t="n">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="E413" s="3" t="n">
         <v>0</v>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C414" s="3" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D414" s="3" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="E414" s="3" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C415" s="3" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D415" s="3" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E415" s="3" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C416" s="3" t="n">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="D416" s="3" t="n">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="E416" s="3" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C417" s="3" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D417" s="3" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="E417" s="3" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C418" s="3" t="n">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="D418" s="3" t="n">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="E418" s="3" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C419" s="3" t="n">
-        <v>151</v>
+        <v>46</v>
       </c>
       <c r="D419" s="3" t="n">
-        <v>151</v>
+        <v>46</v>
       </c>
       <c r="E419" s="3" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C420" s="3" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D420" s="3" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E420" s="3" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C421" s="3" t="n">
-        <v>58</v>
+        <v>151</v>
       </c>
       <c r="D421" s="3" t="n">
-        <v>58</v>
+        <v>151</v>
       </c>
       <c r="E421" s="3" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C422" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D422" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E422" s="3" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C423" s="3" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D423" s="3" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E423" s="3" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C424" s="3" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D424" s="3" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E424" s="3" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C425" s="3" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D425" s="3" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E425" s="3" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C426" s="3" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="D426" s="3" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E426" s="3" t="n">
         <v>0</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C427" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D427" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E427" s="3" t="n">
         <v>0</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C428" s="3" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="D428" s="3" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="E428" s="3" t="n">
         <v>0</v>
@@ -9909,59 +9909,59 @@
       </c>
       <c r="B429" s="3" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C429" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D429" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E429" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B430" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C430" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D430" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E430" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B431" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C429" s="3" t="n">
+      <c r="C431" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D429" s="3" t="n">
+      <c r="D431" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="E429" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B430" s="4" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C430" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="D430" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="E430" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B431" s="4" t="inlineStr">
-        <is>
-          <t>广西</t>
-        </is>
-      </c>
-      <c r="C431" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="D431" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="E431" s="4" t="n">
-        <v>1</v>
+      <c r="E431" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="432">
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C432" s="4" t="n">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="D432" s="4" t="n">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="E432" s="4" t="n">
         <v>1</v>
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C433" s="4" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="D433" s="4" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="E433" s="4" t="n">
         <v>1</v>
@@ -10014,16 +10014,58 @@
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="C434" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="D434" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="E434" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B435" s="4" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="C435" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="D435" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="E435" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B436" s="4" t="inlineStr">
+        <is>
           <t>重庆</t>
         </is>
       </c>
-      <c r="C434" s="4" t="n">
+      <c r="C436" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="D434" s="4" t="n">
+      <c r="D436" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="E434" s="4" t="n">
+      <c r="E436" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10218,7 +10260,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10233,7 +10275,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10287,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10260,7 +10302,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10557,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10530,7 +10572,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10584,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10557,7 +10599,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10821,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10794,7 +10836,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10848,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10821,7 +10863,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10875,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10848,7 +10890,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10929,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10902,7 +10944,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
     </row>
@@ -11557,22 +11599,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11582,29 +11624,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11614,7 +11656,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
@@ -11626,17 +11668,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11646,29 +11688,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11678,7 +11720,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
@@ -11690,17 +11732,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11710,29 +11752,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11742,29 +11784,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11774,29 +11816,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11806,7 +11848,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11818,17 +11860,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11838,29 +11880,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11870,14 +11912,14 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -11887,12 +11929,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11902,29 +11944,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11934,7 +11976,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -11946,17 +11988,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11966,29 +12008,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11998,29 +12040,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12030,7 +12072,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
@@ -12069,22 +12111,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12133,22 +12175,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12207,12 +12249,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12229,22 +12271,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12266,17 +12308,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12293,22 +12335,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（33家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（25条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（33家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（25条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -11604,17 +11604,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
@@ -11636,17 +11636,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11656,29 +11656,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -11700,17 +11700,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
@@ -11732,17 +11732,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11752,29 +11752,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11784,29 +11784,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11816,29 +11816,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -11887,22 +11887,22 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11912,29 +11912,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11944,29 +11944,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11988,17 +11988,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12008,29 +12008,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12040,14 +12040,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -12111,22 +12111,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12143,22 +12143,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12175,22 +12175,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12207,22 +12207,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12239,22 +12239,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12271,7 +12271,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -12281,12 +12281,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12303,22 +12303,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12335,22 +12335,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10557,7 +10557,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
     </row>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
     </row>
@@ -11599,22 +11599,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11624,29 +11624,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11656,29 +11656,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11688,29 +11688,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11720,29 +11720,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11752,29 +11752,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11784,29 +11784,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11816,14 +11816,14 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -11833,12 +11833,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11848,29 +11848,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
@@ -11892,17 +11892,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11912,29 +11912,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11944,29 +11944,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11976,29 +11976,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12008,29 +12008,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -12052,17 +12052,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
@@ -12148,17 +12148,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12207,7 +12207,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -12217,12 +12217,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12239,22 +12239,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12271,22 +12271,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12335,22 +12335,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（18家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（33家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（25条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（17家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（32家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（26条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,14 +665,14 @@
         <v>865</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.5%</t>
         </is>
       </c>
     </row>
@@ -851,17 +851,17 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1717</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
     </row>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8736</v>
+        <v>8737</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8721</v>
+        <v>8722</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-15</v>
@@ -4491,17 +4491,17 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="172">
@@ -4512,14 +4512,14 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="E172" s="2" t="n">
         <v>-1</v>
@@ -4533,14 +4533,14 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E173" s="2" t="n">
         <v>-1</v>
@@ -4554,14 +4554,14 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="E174" s="2" t="n">
         <v>-1</v>
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="C436" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D436" s="4" t="n">
         <v>44</v>
       </c>
       <c r="E436" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -10080,7 +10080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10088,6 +10088,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10116,6 +10117,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -10143,6 +10149,11 @@
           <t>天津市西青区大寺镇兴业道18号</t>
         </is>
       </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -10170,6 +10181,11 @@
           <t>吉林大街518号吉林昌邑万达广场室内步行街1F层</t>
         </is>
       </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -10197,6 +10213,11 @@
           <t>上高路186号</t>
         </is>
       </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -10224,6 +10245,11 @@
           <t>爱情海购物中心18号3幢</t>
         </is>
       </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -10251,6 +10277,11 @@
           <t>吉林省长春市南关区净月开发区天宇路555号</t>
         </is>
       </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -10278,6 +10309,11 @@
           <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -10305,6 +10341,11 @@
           <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -10332,6 +10373,11 @@
           <t>安徽省合肥市蜀山区潜山路111号合肥万象城L127号</t>
         </is>
       </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -10359,6 +10405,11 @@
           <t>山东省东营市垦利区北二路9号</t>
         </is>
       </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -10386,6 +10437,11 @@
           <t>江苏省苏州市吴中区木渎镇中山东路153号</t>
         </is>
       </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -10413,6 +10469,11 @@
           <t>浙江省绍兴市越城区灵芝街道解放大道190号苏宁广场第一层113C号商铺</t>
         </is>
       </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -10440,6 +10501,11 @@
           <t>云南省昆明市西山区滇池路569号南亚风情第壹城F1华为智能生活馆</t>
         </is>
       </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -10467,6 +10533,11 @@
           <t>广东省深圳市宝安区107国道西乡段371号</t>
         </is>
       </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -10494,6 +10565,11 @@
           <t>中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -10521,6 +10597,11 @@
           <t>河南省商丘市梁园区锦绣路与金桥路交叉口北200米路西</t>
         </is>
       </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260601，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -10548,6 +10629,11 @@
           <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
         </is>
       </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260601，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -10557,7 +10643,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10572,34 +10658,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
           <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10614,7 +10678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10622,6 +10686,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10650,6 +10715,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -10677,6 +10747,11 @@
           <t>宝安区西乡街道宝安大道与海城路交汇处QCC一期一层</t>
         </is>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -10704,6 +10779,11 @@
           <t>山东省菏泽市定陶区汽车小镇（广州路与向阳路交叉路口东北角）</t>
         </is>
       </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -10731,6 +10811,11 @@
           <t>河北省保定市清苑区振清南街806号</t>
         </is>
       </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -10758,6 +10843,11 @@
           <t>河南省新乡市红旗区新长北路东安汽车园</t>
         </is>
       </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -10785,6 +10875,11 @@
           <t>河南省郑州市郑东新区商都路与东三环交汇处东200米</t>
         </is>
       </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -10812,6 +10907,11 @@
           <t>福建省厦门市集美区岩兴路89号</t>
         </is>
       </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -10821,7 +10921,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10836,7 +10936,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10953,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10863,7 +10968,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10985,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10890,7 +11000,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
@@ -10902,7 +11017,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10917,7 +11032,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>国瑞城一层中庭</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
@@ -10929,7 +11049,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10944,7 +11064,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
@@ -10974,6 +11099,11 @@
           <t>安徽省淮南市田家庵区洞山东路8号吾悦广场</t>
         </is>
       </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -11001,6 +11131,11 @@
           <t>章丘世茂广场1楼中庭</t>
         </is>
       </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -11028,6 +11163,11 @@
           <t>开发区万达广场1楼中庭</t>
         </is>
       </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -11055,6 +11195,11 @@
           <t>山东省聊城市东昌府区柳园北路39号万达广场1楼</t>
         </is>
       </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -11082,6 +11227,11 @@
           <t>凯德广场华鑫城购物中心1F中庭</t>
         </is>
       </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -11109,6 +11259,11 @@
           <t>创新大道15号永旺梦乐城1楼迎宾广场</t>
         </is>
       </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -11136,6 +11291,11 @@
           <t>新疆维吾尔自治区巴音郭楞蒙古自治州库尔勒市团结辖区朝阳路9号</t>
         </is>
       </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -11145,22 +11305,27 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏太百购物中心</t>
+          <t>小米汽车浙江嘉兴海盐县海盐吾悦广场</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>阿克苏地区</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区阿克苏地区阿克苏市新华东路33-1号</t>
+          <t>浙江省嘉兴市海盐县枣园路吾悦广场一楼一号门处</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
@@ -11172,7 +11337,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴海盐县海盐吾悦广场</t>
+          <t>小米汽车浙江宁波市宁海县西子国际</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -11182,12 +11347,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市</t>
+          <t>宁波市</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海盐县枣园路吾悦广场一楼一号门处</t>
+          <t>浙江省宁波市宁海县西子国际购物中心北中庭（华为旁）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11199,7 +11369,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市宁海县西子国际</t>
+          <t>小米汽车浙江舟山定海区舟山宝龙广场</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -11209,12 +11379,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>宁波市</t>
+          <t>舟山市</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市宁海县西子国际购物中心北中庭（华为旁）</t>
+          <t>定沈路699号(特斯拉展位边)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
@@ -11226,49 +11401,59 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江舟山定海区舟山宝龙广场</t>
+          <t>小米汽车陕西西安未央区西安西咸万象城</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>舟山市</t>
+          <t>西安市</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>定沈路699号(特斯拉展位边)</t>
+          <t>三桥新街1076号万象城中庭CAL1-012</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车陕西西安未央区西安西咸万象城</t>
+          <t>小鹏汽车淄博山泉路汽车城销售服务中心</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>西安市</t>
+          <t>淄博市</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>三桥新街1076号万象城中庭CAL1-012</t>
+          <t>淄博市张店区山泉路89号</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 5 期</t>
         </is>
       </c>
     </row>
@@ -11280,22 +11465,27 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车淄博山泉路汽车城销售服务中心</t>
+          <t>小鹏汽车佛山顺德悦然广场销售展厅</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>淄博市</t>
+          <t>佛山市</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>淄博市张店区山泉路89号</t>
+          <t>佛山市顺德区北滘镇美的悦然广场L1/1023号铺(迪卡侬旁)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
@@ -11307,49 +11497,59 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德悦然广场销售展厅</t>
+          <t>小鹏汽车绍兴万悦城销售中心</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>佛山市</t>
+          <t>绍兴市</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘镇美的悦然广场L1/1023号铺(迪卡侬旁)</t>
+          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴万悦城销售中心</t>
+          <t>深圳罗湖KKMALL体验店</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>绍兴市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>广东省深圳市罗湖区桂园街道深南东路5016号KKMALL一层L112/112A3</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
@@ -11361,22 +11561,27 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>深圳罗湖KKMALL体验店</t>
+          <t>贵阳方圆荟海豚广场</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市罗湖区桂园街道深南东路5016号KKMALL一层L112/112A3</t>
+          <t>贵州省贵阳市南明区花果园大街88号1F-SN007铺位</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
@@ -11388,49 +11593,59 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>贵阳方圆荟海豚广场</t>
+          <t>西安曲江大悦城体验店</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>西安市</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>贵州省贵阳市南明区花果园大街88号1F-SN007铺位</t>
+          <t>陕西省西安市雁塔区慈恩西路777号</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>西安曲江大悦城体验店</t>
+          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>西安市</t>
+          <t>威海市</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>陕西省西安市雁塔区慈恩西路777号</t>
+          <t>山东省威海市环翠区经技技术开发区青岛南路242号</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
@@ -11442,22 +11657,27 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
+          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>威海市</t>
+          <t>晋中市</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>山东省威海市环翠区经技技术开发区青岛南路242号</t>
+          <t>山西省晋中市山西综改示范区晋中开发区汇通产业园区汇通北路1060号</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
@@ -11469,22 +11689,27 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
+          <t>鸿蒙智行授权用户中心•东莞虎门鸿熙汽车城</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>东莞市</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>山西省晋中市山西综改示范区晋中开发区汇通产业园区汇通北路1060号</t>
+          <t>广东省东莞市虎门镇博涌社区社岗村S358省道旁</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 1 期</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11721,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•东莞虎门鸿熙汽车城</t>
+          <t>华为授权体验店（新塘永旺）</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11506,39 +11731,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>东莞市</t>
+          <t>广州市</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>广东省东莞市虎门镇博涌社区社岗村S358省道旁</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>华为授权体验店（新塘永旺）</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
           <t>广东省广州市增城区新塘永旺1楼华为授权体验店（西町村屋对面）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>连续在档 6 期</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11599,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11624,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11656,7 +11859,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
@@ -11668,17 +11871,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11688,29 +11891,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11720,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11752,29 +11955,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11784,29 +11987,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11816,29 +12019,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11848,29 +12051,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11880,7 +12083,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -11892,17 +12095,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11912,29 +12115,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11944,29 +12147,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11976,29 +12179,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12008,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12040,29 +12243,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12072,93 +12275,93 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京紫金山科技城交付中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京紫金山科技城销售展厅</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京紫金山科技城交付中心 → 小鹏汽车南京紫金山科技城销售展厅</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>小鹏汽车南京紫金山科技城交付中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>小鹏汽车南京紫金山科技城销售展厅</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>地址归一前缀一致</t>
+          <t>小鹏汽车南京紫金山科技城交付中心 → 小鹏汽车南京紫金山科技城销售展厅</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12175,7 +12378,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -12185,12 +12388,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12207,7 +12410,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -12217,12 +12420,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12276,17 +12479,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12303,22 +12506,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12340,17 +12543,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12372,25 +12575,57 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>华为授权体验店（西溪印象城）</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>华为智能生活馆•杭州西溪印象城</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>地址变更</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>地址归一前缀一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
           <t>安徽</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>华为智能生活馆•蚌埠银泰百货</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>地址变更</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>地址相似度 80%</t>
         </is>

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10686,7 +10686,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>连续在档 5 期</t>
+          <t>连续在档 5 期；本期存在高相似店名「(新)小鹏汽车淄博山泉路汽车城销售服务中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>连续在档 6 期</t>
+          <t>连续在档 6 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>连续在档 6 期</t>
+          <t>连续在档 6 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>华为旗舰店•南昌万象城</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,29 +12051,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,29 +12147,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -12287,17 +12287,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
         </is>
       </c>
     </row>
@@ -12346,7 +12346,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12442,22 +12442,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12474,22 +12474,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12511,17 +12511,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12538,7 +12538,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -12548,12 +12548,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -9,9 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（17家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（32家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（26条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（13家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（30家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（22条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,23 +845,23 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
-        <v>1715</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1717</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>0.1%</t>
+      <c r="B18" s="3" t="n">
+        <v>1458</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1458</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -872,13 +872,13 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8737</v>
+        <v>8480</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8722</v>
+        <v>8463</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-15</v>
+        <v>-17</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
@@ -9426,59 +9426,59 @@
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C406" s="2" t="n">
-        <v>101</v>
+        <v>182</v>
       </c>
       <c r="D406" s="2" t="n">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="E406" s="2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="inlineStr">
+      <c r="A407" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B407" s="2" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C407" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="D407" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="E407" s="2" t="n">
-        <v>-1</v>
+      <c r="B407" s="3" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C407" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="D407" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="E407" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="inlineStr">
+      <c r="A408" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B408" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C408" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="D408" s="2" t="n">
-        <v>204</v>
-      </c>
-      <c r="E408" s="2" t="n">
-        <v>-1</v>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="C408" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D408" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E408" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="409">
@@ -9489,14 +9489,14 @@
       </c>
       <c r="B409" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C409" s="3" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="D409" s="3" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="E409" s="3" t="n">
         <v>0</v>
@@ -9510,14 +9510,14 @@
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C410" s="3" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D410" s="3" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E410" s="3" t="n">
         <v>0</v>
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C411" s="3" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="D411" s="3" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="E411" s="3" t="n">
         <v>0</v>
@@ -9552,7 +9552,7 @@
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C412" s="3" t="n">
@@ -9573,14 +9573,14 @@
       </c>
       <c r="B413" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C413" s="3" t="n">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="D413" s="3" t="n">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="E413" s="3" t="n">
         <v>0</v>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C414" s="3" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D414" s="3" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="E414" s="3" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C415" s="3" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="D415" s="3" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="E415" s="3" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C416" s="3" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D416" s="3" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="E416" s="3" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C417" s="3" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D417" s="3" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E417" s="3" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C418" s="3" t="n">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c r="D418" s="3" t="n">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c r="E418" s="3" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C419" s="3" t="n">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="D419" s="3" t="n">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="E419" s="3" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C420" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D420" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E420" s="3" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C421" s="3" t="n">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="D421" s="3" t="n">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="E421" s="3" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C422" s="3" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="D422" s="3" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="E422" s="3" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C423" s="3" t="n">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="D423" s="3" t="n">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="E423" s="3" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C424" s="3" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D424" s="3" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E424" s="3" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C425" s="3" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D425" s="3" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E425" s="3" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C426" s="3" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D426" s="3" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E426" s="3" t="n">
         <v>0</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C427" s="3" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D427" s="3" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E427" s="3" t="n">
         <v>0</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C428" s="3" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="D428" s="3" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E428" s="3" t="n">
         <v>0</v>
@@ -9909,14 +9909,14 @@
       </c>
       <c r="B429" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C429" s="3" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D429" s="3" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E429" s="3" t="n">
         <v>0</v>
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C430" s="3" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D430" s="3" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E430" s="3" t="n">
         <v>0</v>
@@ -9951,80 +9951,80 @@
       </c>
       <c r="B431" s="3" t="inlineStr">
         <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C431" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D431" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E431" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B432" s="3" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C432" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D432" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="E432" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B433" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C433" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D433" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E433" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B434" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C431" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="D431" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="E431" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B432" s="4" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C432" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="D432" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="E432" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B433" s="4" t="inlineStr">
-        <is>
-          <t>广西</t>
-        </is>
-      </c>
-      <c r="C433" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="D433" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="E433" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B434" s="4" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C434" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="D434" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="E434" s="4" t="n">
-        <v>1</v>
+      <c r="C434" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D434" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E434" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="435">
@@ -10035,14 +10035,14 @@
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C435" s="4" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="D435" s="4" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="E435" s="4" t="n">
         <v>1</v>
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="C436" s="4" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D436" s="4" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E436" s="4" t="n">
         <v>1</v>
@@ -10080,7 +10080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10088,7 +10088,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10515,153 +10515,25 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•深圳宝安鸿友汽车园</t>
+          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区107国道西乡段371号</t>
+          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行享界用户中心•南宁五象钜荣汽车园</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>广西</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>南宁市</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•商丘金桥北路</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>商丘市</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>河南省商丘市梁园区锦绣路与金桥路交叉口北200米路西</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260601，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>邵阳市</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260601，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•重庆龙湖礼嘉天街</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>重庆市两江新区礼慈路14号龙湖重庆礼嘉天街A馆1F-29、30、31、32号</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>全新</t>
         </is>
@@ -10678,7 +10550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10953,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10968,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10985,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -11000,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -11625,27 +11497,27 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•威海青岛南路</t>
+          <t>鸿蒙智行授权用户中心•东莞虎门鸿熙汽车城</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>威海市</t>
+          <t>东莞市</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>山东省威海市环翠区经技技术开发区青岛南路242号</t>
+          <t>广东省东莞市虎门镇博涌社区社岗村S358省道旁</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>连续在档 6 期；本期同名店仍在档（地址写法变更，非关店）</t>
+          <t>连续在档 1 期</t>
         </is>
       </c>
     </row>
@@ -11657,89 +11529,25 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•晋中汇通北路</t>
+          <t>华为授权体验店（新塘永旺）</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>晋中市</t>
+          <t>广州市</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>山西省晋中市山西综改示范区晋中开发区汇通产业园区汇通北路1060号</t>
+          <t>广东省广州市增城区新塘永旺1楼华为授权体验店（西町村屋对面）</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 6 期；本期同名店仍在档（地址写法变更，非关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•东莞虎门鸿熙汽车城</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>东莞市</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>广东省东莞市虎门镇博涌社区社岗村S358省道旁</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>连续在档 1 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>华为授权体验店（新塘永旺）</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>广州市</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>广东省广州市增城区新塘永旺1楼华为授权体验店（西町村屋对面）</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>连续在档 6 期</t>
         </is>
@@ -11756,7 +11564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11807,17 +11615,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•长春景阳大路</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>吉林省长春市汽开区景阳大路3862号 → 吉林省长春市绿园区景阳大路3862号</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为旗舰店•南昌万象城</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,7 +11667,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市红谷滩区学府大道388号的南昌万象城L150、L259号商铺 → 江西省南昌市红谷滩区学府大道388号的南昌万象城L149-L150，L259号商铺</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11731,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳宝安创业二路</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市宝安区新安街道大浪社区创业二路195号 → 广东省深圳市宝安区新安街道大宝路60号鸿蒙智行用户中心·深圳宝安创业二路</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,7 +11827,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -12031,17 +11839,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,29 +11859,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,29 +11891,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,7 +11923,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
@@ -12127,17 +11935,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,29 +11955,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -12191,49 +11999,49 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车南京紫金山科技城交付中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车南京紫金山科技城销售展厅</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>小鹏汽车南京紫金山科技城交付中心 → 小鹏汽车南京紫金山科技城销售展厅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,29 +12051,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,29 +12083,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•镇江丁卯汽车城</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12307,39 +12115,39 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省镇江市京口区丁卯经十二路658号（临时营业） → 江苏省镇江市京口区新区丁卯经十二路658号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京紫金山科技城交付中心</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京紫金山科技城销售展厅</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京紫金山科技城交付中心 → 小鹏汽车南京紫金山科技城销售展厅</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
@@ -12351,17 +12159,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12378,7 +12186,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -12388,12 +12196,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12410,22 +12218,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12442,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12479,17 +12287,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>华为智能生活馆•蚌埠银泰城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>华为智能生活馆•蚌埠银泰百货</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12498,134 +12306,6 @@
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>杭州广沃4S中心</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>AITO授权用户中心•台州路桥</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•蚌埠银泰城</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•蚌埠银泰百货</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>地址相似度 80%</t>
         </is>

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>0</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8480</v>
+        <v>8479</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8463</v>
+        <v>8462</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-17</v>
@@ -9913,10 +9913,10 @@
         </is>
       </c>
       <c r="C429" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D429" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E429" s="3" t="n">
         <v>0</v>
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,29 +11763,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11962,22 +11962,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
@@ -12058,22 +12058,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12122,22 +12122,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12154,7 +12154,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12218,22 +12218,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（13家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（30家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（22条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（13家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（30家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（22条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,29 +11763,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
@@ -11898,7 +11898,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -12026,22 +12026,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12058,7 +12058,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12090,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12154,22 +12154,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12186,22 +12186,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12218,7 +12218,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,29 +11731,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,29 +11763,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12026,22 +12026,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12058,22 +12058,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12090,7 +12090,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12154,22 +12154,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12186,22 +12186,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12218,22 +12218,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（13家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（30家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（22条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（13家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（30家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（22条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,29 +11731,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -11807,17 +11807,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -12026,22 +12026,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12090,7 +12090,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12154,7 +12154,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（13家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（30家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（22条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（13家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（30家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（22条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,29 +11731,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
@@ -11802,22 +11802,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12090,7 +12090,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12154,22 +12154,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12186,22 +12186,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12218,22 +12218,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11642,22 +11642,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
@@ -11770,22 +11770,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12026,22 +12026,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12090,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12154,22 +12154,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12186,22 +12186,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12250,7 +12250,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃临平卫星店</t>
+          <t>杭州广沃钱塘新能源体验中心</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市临平区新天路176号1幢103室</t>
+          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>杭州广沃钱塘新能源体验中心</t>
+          <t>杭州广沃临平卫星店</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>浙江省杭州市钱塘区下沙街道德胜东路2399号1号楼1层17-2号</t>
+          <t>浙江省杭州市临平区新天路176号1幢103室</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
@@ -11738,22 +11738,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,29 +11763,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11807,17 +11807,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
@@ -12026,22 +12026,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12058,22 +12058,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12127,17 +12127,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12154,7 +12154,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京东城区国瑞城</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>国瑞城一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京东城区国瑞城</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>国瑞城一层中庭</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（桥西勒泰）</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,29 +11699,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>华为授权体验店（桥西勒泰）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>河北省石家庄市桥西区西里街道槐安西路255号勒泰广场1层 → 河北省石家庄市桥西区西里街道槐安西路255号勒泰广场一层</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
@@ -12026,22 +12026,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12058,22 +12058,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12090,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12122,7 +12122,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12154,22 +12154,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12223,17 +12223,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260608_vs_20260615.xlsx
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区乐多港万达</t>
+          <t>小米汽车北京昌平区首开Long街</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>昌平乐多港万达一层中庭</t>
+          <t>首开Long街南区室外一层中庭</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区远洋乐堤港</t>
+          <t>小米汽车北京大兴区亦庄龙湖天街</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>远洋乐堤港一层中庭</t>
+          <t>亦庄龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京大兴区亦庄龙湖天街</t>
+          <t>小米汽车北京通州区远洋乐堤港</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>亦庄龙湖天街一层中庭</t>
+          <t>远洋乐堤港一层中庭</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区首开Long街</t>
+          <t>小米汽车北京昌平区乐多港万达</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>首开Long街南区室外一层中庭</t>
+          <t>昌平乐多港万达一层中庭</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -11610,22 +11610,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小鹏汽车福州鼓楼销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
+          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（悦荟）</t>
+          <t>库尔勒万宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
+          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>华为授权体验店（悦荟）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>重庆市江北区红石路331号附3号重庆悦荟UGA48、UGA49、UGA50-2 → 重庆市两江新区红石路331号附3号重庆悦荟UGA48UGA49UGA50-2</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
+          <t>小鹏汽车抚州临川大道服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11731,29 +11731,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
+          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海口南海大道销售服务中心</t>
+          <t>蔚来空间 | 武汉黄浦科技园</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
+          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车抚州临川大道服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>抚州市临川区临川大道小鹏服务中心 → 抚州市临川区临川大道小鹏交付中心</t>
+          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>库尔勒万宝行汽车销售服务有限公司</t>
+          <t>上汽奥迪南通百尊用户中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区库尔勒市石化大道北侧神州国际汽车城   841000 → 新疆巴州库尔勒市梨乡辖区石化大道213号深蓝宝马厅17栋1至2层1号   841000</t>
+          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车福州鼓楼销售服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>福建省福州市鼓楼区杨桥中路277号 → 杨桥中路277号</t>
+          <t>红谷滩区碟子湖大道366号 → 红谷滩区碟子湖大道366号一层01商铺</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车海口南海大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车交付中心 → 青岛市市北区大沙路2号青岛青锋国际汽车城小鹏汽车展厅</t>
+          <t>海南省海口市龙华区南海大道115号 → 海南省海口市龙华区南海大道115号福德汽车城小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11930,22 +11930,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 武汉黄浦科技园</t>
+          <t>小鹏汽车绍兴上虞汽车城销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼 → 湖北省武汉市江岸区后湖街石桥辖区工业园工业产房1号楼一楼蔚来汽车展厅(平安健康检测中心旁)</t>
+          <t>浙江省绍兴市上虞区迎宾大道与边沥交叉口东北420米 → 浙江省绍兴市上虞区五星东路8号万悦城广场137+146号铺位</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪南通百尊用户中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>星湖大道1008号 → 江苏省南通市开发区竹行街道星湖大道1008号</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -12026,22 +12026,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪兰州中盛奥泽用户中心</t>
+          <t>杭州广沃4S中心（过渡运营）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>甘肃中盛奥泽</t>
+          <t>杭州广沃4S中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12058,7 +12058,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 广州番禺桥南</t>
+          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 广州番禺桥南</t>
+          <t>鸿蒙智行授权用户中心•佛山大道</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12090,22 +12090,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（西溪印象城）</t>
+          <t>蔚来体验中心 | 济南工业北路</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•杭州西溪印象城</t>
+          <t>蔚来空间 | 济南工业北路</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12122,7 +12122,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心（过渡运营）</t>
+          <t>AITO授权用户中心•台州F7汽车广场</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>杭州广沃4S中心</t>
+          <t>AITO授权用户中心•台州路桥</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12154,22 +12154,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>蔚来体验中心 | 济南工业北路</t>
+          <t>华为智能生活馆•宁波环球银泰城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南工业北路</t>
+          <t>华为智能生活馆•宁波环球银泰百货</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12186,22 +12186,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰城</t>
+          <t>蔚来体验中心 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•宁波环球银泰百货</t>
+          <t>蔚来空间 | 广州番禺桥南</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州F7汽车广场</t>
+          <t>华为授权体验店（西溪印象城）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•台州路桥</t>
+          <t>华为智能生活馆•杭州西溪印象城</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12250,22 +12250,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山禅城大道</t>
+          <t>上汽奥迪兰州中盛奥泽用户中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•佛山大道</t>
+          <t>甘肃中盛奥泽</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
